--- a/StructureDefinition-intraocular-pressure.xlsx
+++ b/StructureDefinition-intraocular-pressure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T20:04:06+00:00</t>
+    <t>2026-08-19T17:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-intraocular-pressure.xlsx
+++ b/StructureDefinition-intraocular-pressure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T17:13:42+00:00</t>
+    <t>2026-08-19T17:55:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-intraocular-pressure.xlsx
+++ b/StructureDefinition-intraocular-pressure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T17:55:33+00:00</t>
+    <t>2026-08-25T00:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-intraocular-pressure.xlsx
+++ b/StructureDefinition-intraocular-pressure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T00:41:24+00:00</t>
+    <t>2026-08-25T02:25:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-intraocular-pressure.xlsx
+++ b/StructureDefinition-intraocular-pressure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T02:25:39+00:00</t>
+    <t>2026-08-25T18:52:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-intraocular-pressure.xlsx
+++ b/StructureDefinition-intraocular-pressure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T18:52:20+00:00</t>
+    <t>2026-09-01T17:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -286,7 +286,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}inv-iop-range:IOP value must be between 0 and 80 mmHg {valueQuantity.value &gt;= 0 and valueQuantity.value &lt;= 80}</t>
   </si>
   <si>
     <t>Event</t>
